--- a/tricount_extractor/tests/data/expected_results/custom_category_trip_8.xlsx
+++ b/tricount_extractor/tests/data/expected_results/custom_category_trip_8.xlsx
@@ -952,7 +952,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -965,7 +965,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/tricount_extractor/tests/data/expected_results/custom_category_trip_8.xlsx
+++ b/tricount_extractor/tests/data/expected_results/custom_category_trip_8.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,11 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>is_income</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>category</t>
         </is>
       </c>
@@ -597,7 +602,10 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>my custom label</t>
         </is>
@@ -642,7 +650,10 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>UNCATEGORIZED</t>
         </is>
@@ -659,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,25 +701,30 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>is_income</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>participant</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>original_share</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>original_currency</t>
         </is>
@@ -737,23 +753,26 @@
       <c r="F2" t="b">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>25</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>25</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -782,23 +801,26 @@
       <c r="F3" t="b">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>25</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>25</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -827,23 +849,26 @@
       <c r="F4" t="b">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>15</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>15</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -872,23 +897,26 @@
       <c r="F5" t="b">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>15</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>15</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>

--- a/tricount_extractor/tests/data/expected_results/custom_category_trip_8.xlsx
+++ b/tricount_extractor/tests/data/expected_results/custom_category_trip_8.xlsx
@@ -12,6 +12,7 @@
     <sheet name="allocations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="attachments" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="balances" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="transaction_ledger" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -503,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +555,11 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>is_income</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>category</t>
         </is>
       </c>
@@ -597,7 +603,10 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>my custom label</t>
         </is>
@@ -642,7 +651,10 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>UNCATEGORIZED</t>
         </is>
@@ -659,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,25 +702,30 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>is_income</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>participant</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>original_share</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>original_currency</t>
         </is>
@@ -737,23 +754,26 @@
       <c r="F2" t="b">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>25</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>25</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -782,23 +802,26 @@
       <c r="F3" t="b">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>25</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>25</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -827,23 +850,26 @@
       <c r="F4" t="b">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>15</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>15</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -872,23 +898,26 @@
       <c r="F5" t="b">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>15</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>15</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -975,4 +1004,138 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Custom Category Expense</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>my custom label</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Regular Expense</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UNCATEGORIZED</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>